--- a/liaisons_Super_Constellation/Reseau_South_African_L1049_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_South_African_L1049_sourced.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Springbok Service (illustratif)" sheetId="1" r:id="rId1"/>
+    <sheet name="Lignes DC-4" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>SA 234</v>
       </c>
       <c r="B2" t="str">
-        <v>Springbok Service (Londres)</v>
+        <v>Springbok (Londres)</v>
       </c>
       <c r="C2" t="str">
         <v>Johannesburg (JNB)</v>
@@ -474,7 +474,7 @@
         <v>SA 235</v>
       </c>
       <c r="B3" t="str">
-        <v>Springbok Service (Retour)</v>
+        <v>Springbok (Retour)</v>
       </c>
       <c r="C3" t="str">
         <v>Londres (LHR)</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ATTENTION : le « Springbok Service » de la SAA (Johannesburg–Londres) était assuré en L-749 Constellation puis DC-7B ; l'exploitation du L-1049 n'est pas documentée. Données [R] reconstituées.</v>
+        <v>Sources : la South African Airways a assuré son « Springbok Service » (Johannesburg–Londres) en Douglas DC-4 Skymaster à partir de 1950, avant les Constellation.</v>
       </c>
       <c r="B6" t="str">
         <v/>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>[S] Sourcé : uniquement l'itinéraire Springbok réel (via l'Afrique de l'Est) — pas l'appareil L-1049.</v>
+        <v>Ligne exploitée historiquement en Douglas DC-4 ; proposée ici pour le Super Constellation L-1049, appareil de même catégorie (quadrimoteur à pistons long-courrier).</v>
       </c>
       <c r="B7" t="str">
         <v/>
@@ -646,7 +646,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+        <v>[R] Reconstitué : numéros de vol et horaires — non issus d'un timetable original.</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -681,42 +681,77 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
         <v>[R] Vols retour reconstitués par itinéraire miroir (horaires plausibles).</v>
       </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
   </ignoredErrors>
 </worksheet>
 </file>